--- a/Sprint 10/dades_GrupD.xlsx
+++ b/Sprint 10/dades_GrupD.xlsx
@@ -4553,7 +4553,7 @@
         <v>38282</v>
       </c>
       <c r="P53" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>

--- a/Sprint 10/dades_GrupD.xlsx
+++ b/Sprint 10/dades_GrupD.xlsx
@@ -1293,7 +1293,7 @@
         <v>38657</v>
       </c>
       <c r="P11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>36833</v>
       </c>
       <c r="P24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>38285</v>
       </c>
       <c r="P56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
